--- a/counselor_forms/031_placement_feedback_form--counselor_forms.xlsx
+++ b/counselor_forms/031_placement_feedback_form--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'counselor_1'}</t>
+          <t>counselor_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor 1'}</t>
+          <t>Counselor 1</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'counselor_2'}</t>
+          <t>counselor_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor 2'}</t>
+          <t>Counselor 2</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'counselor_3'}</t>
+          <t>counselor_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor 3'}</t>
+          <t>Counselor 3</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'highly_dissatisfied'}</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Dissatisfied'}</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'highly_dissatisfied'}</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Dissatisfied'}</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'highly_dissatisfied'}</t>
+          <t>highly_dissatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Dissatisfied'}</t>
+          <t>Highly Dissatisfied</t>
         </is>
       </c>
     </row>
